--- a/383Game/Doc/Brain Stew Master Gantt Chart.xlsx
+++ b/383Game/Doc/Brain Stew Master Gantt Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aneeshashrestha/Documents/GitHub/CS383BrainstewGame/383Game/Doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/19db3ad368368567/Documents/GitHub/CS383BrainstewGame/383Game/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97EFEB6-BC69-234F-B622-F5F1D74BC570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B97EFEB6-BC69-234F-B622-F5F1D74BC570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{175BDC0A-5F49-42F2-AB8F-A6A1BD7DF35B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="1" r:id="rId1"/>
@@ -1003,7 +1003,49 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1024,59 +1066,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1340,578 +1340,669 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:AF22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="10.6640625" customWidth="1"/>
     <col min="17" max="17" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="76" t="s">
+    <row r="2" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="K2" s="76" t="s">
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="K2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="S2" s="76" t="s">
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="S2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="76"/>
-      <c r="AA2" s="76" t="s">
+      <c r="T2" s="90"/>
+      <c r="U2" s="90"/>
+      <c r="V2" s="90"/>
+      <c r="W2" s="90"/>
+      <c r="X2" s="90"/>
+      <c r="AA2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="76"/>
-      <c r="AC2" s="76"/>
-      <c r="AD2" s="76"/>
-      <c r="AE2" s="76"/>
-      <c r="AF2" s="76"/>
-    </row>
-    <row r="3" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="77" t="s">
+      <c r="AB2" s="90"/>
+      <c r="AC2" s="90"/>
+      <c r="AD2" s="90"/>
+      <c r="AE2" s="90"/>
+      <c r="AF2" s="90"/>
+    </row>
+    <row r="3" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="77"/>
-      <c r="E3" s="78" t="s">
+      <c r="D3" s="91"/>
+      <c r="E3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="78"/>
-      <c r="G3" s="79" t="s">
+      <c r="F3" s="92"/>
+      <c r="G3" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
-      <c r="K3" s="77" t="s">
+      <c r="H3" s="93"/>
+      <c r="K3" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="77"/>
-      <c r="M3" s="78" t="s">
+      <c r="L3" s="91"/>
+      <c r="M3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="78"/>
-      <c r="O3" s="79" t="s">
+      <c r="N3" s="92"/>
+      <c r="O3" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="79"/>
-      <c r="S3" s="77" t="s">
+      <c r="P3" s="93"/>
+      <c r="S3" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="77"/>
-      <c r="U3" s="78" t="s">
+      <c r="T3" s="91"/>
+      <c r="U3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="V3" s="78"/>
-      <c r="W3" s="79" t="s">
+      <c r="V3" s="92"/>
+      <c r="W3" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="X3" s="79"/>
-      <c r="AA3" s="77" t="s">
+      <c r="X3" s="93"/>
+      <c r="AA3" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="AB3" s="77"/>
-      <c r="AC3" s="78" t="s">
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="78"/>
-      <c r="AE3" s="79" t="s">
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="AF3" s="79"/>
-    </row>
-    <row r="4" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF3" s="93"/>
+    </row>
+    <row r="4" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="73">
+      <c r="C4" s="80">
         <v>8200</v>
       </c>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74" t="s">
+      <c r="D4" s="80"/>
+      <c r="E4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75" t="s">
+      <c r="F4" s="88"/>
+      <c r="G4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="89"/>
       <c r="J4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="73">
+      <c r="K4" s="80">
         <v>5200</v>
       </c>
-      <c r="L4" s="73"/>
-      <c r="M4" s="74" t="s">
+      <c r="L4" s="80"/>
+      <c r="M4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="74"/>
-      <c r="O4" s="75" t="s">
+      <c r="N4" s="88"/>
+      <c r="O4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="75"/>
+      <c r="P4" s="89"/>
       <c r="R4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S4" s="73">
+      <c r="S4" s="80">
         <v>3000</v>
       </c>
-      <c r="T4" s="73"/>
-      <c r="U4" s="74" t="s">
+      <c r="T4" s="80"/>
+      <c r="U4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="V4" s="74"/>
-      <c r="W4" s="75" t="s">
+      <c r="V4" s="88"/>
+      <c r="W4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="X4" s="75"/>
+      <c r="X4" s="89"/>
       <c r="Z4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="75"/>
-    </row>
-    <row r="5" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA4" s="87"/>
+      <c r="AB4" s="87"/>
+      <c r="AC4" s="88"/>
+      <c r="AD4" s="88"/>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+    </row>
+    <row r="5" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="73">
+      <c r="C5" s="80">
         <v>10200</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="80" t="s">
+      <c r="D5" s="80"/>
+      <c r="E5" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="80"/>
-      <c r="G5" s="81" t="s">
+      <c r="F5" s="76"/>
+      <c r="G5" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="81"/>
+      <c r="H5" s="85"/>
       <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="83">
+      <c r="K5" s="86">
         <v>7200</v>
       </c>
-      <c r="L5" s="83"/>
-      <c r="M5" s="80" t="s">
+      <c r="L5" s="86"/>
+      <c r="M5" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="80"/>
-      <c r="O5" s="81" t="s">
+      <c r="N5" s="76"/>
+      <c r="O5" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="81"/>
+      <c r="P5" s="85"/>
       <c r="R5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="73">
+      <c r="S5" s="80">
         <v>3000</v>
       </c>
-      <c r="T5" s="73"/>
-      <c r="U5" s="80" t="s">
+      <c r="T5" s="80"/>
+      <c r="U5" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="V5" s="80"/>
-      <c r="W5" s="81" t="s">
+      <c r="V5" s="76"/>
+      <c r="W5" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="81"/>
+      <c r="X5" s="85"/>
       <c r="Z5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="84"/>
       <c r="AB5" s="84"/>
-      <c r="AC5" s="80"/>
-      <c r="AD5" s="80"/>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="81"/>
-    </row>
-    <row r="6" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC5" s="76"/>
+      <c r="AD5" s="76"/>
+      <c r="AE5" s="85"/>
+      <c r="AF5" s="85"/>
+    </row>
+    <row r="6" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="73">
+      <c r="C6" s="80">
         <v>8300</v>
       </c>
-      <c r="D6" s="73"/>
-      <c r="E6" s="80" t="s">
+      <c r="D6" s="80"/>
+      <c r="E6" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="80"/>
-      <c r="G6" s="81" t="s">
+      <c r="F6" s="76"/>
+      <c r="G6" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="81"/>
+      <c r="H6" s="85"/>
       <c r="J6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="83">
+      <c r="K6" s="86">
         <v>5300</v>
       </c>
-      <c r="L6" s="83"/>
-      <c r="M6" s="80" t="s">
+      <c r="L6" s="86"/>
+      <c r="M6" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="81" t="s">
+      <c r="N6" s="76"/>
+      <c r="O6" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="81"/>
+      <c r="P6" s="85"/>
       <c r="R6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S6" s="73">
+      <c r="S6" s="80">
         <v>3000</v>
       </c>
-      <c r="T6" s="73"/>
-      <c r="U6" s="80" t="s">
+      <c r="T6" s="80"/>
+      <c r="U6" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="V6" s="80"/>
-      <c r="W6" s="81" t="s">
+      <c r="V6" s="76"/>
+      <c r="W6" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="X6" s="81"/>
+      <c r="X6" s="85"/>
       <c r="Z6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="AA6" s="84"/>
       <c r="AB6" s="84"/>
-      <c r="AC6" s="80"/>
-      <c r="AD6" s="80"/>
-      <c r="AE6" s="81"/>
-      <c r="AF6" s="81"/>
-    </row>
-    <row r="7" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC6" s="76"/>
+      <c r="AD6" s="76"/>
+      <c r="AE6" s="85"/>
+      <c r="AF6" s="85"/>
+    </row>
+    <row r="7" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="73">
+      <c r="C7" s="80">
         <v>9000</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="80" t="s">
+      <c r="D7" s="80"/>
+      <c r="E7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81" t="s">
+      <c r="F7" s="76"/>
+      <c r="G7" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="81"/>
+      <c r="H7" s="85"/>
       <c r="J7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="83">
+      <c r="K7" s="86">
         <v>6000</v>
       </c>
-      <c r="L7" s="83"/>
-      <c r="M7" s="80" t="s">
+      <c r="L7" s="86"/>
+      <c r="M7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="80"/>
-      <c r="O7" s="81" t="s">
+      <c r="N7" s="76"/>
+      <c r="O7" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="81"/>
+      <c r="P7" s="85"/>
       <c r="R7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="80">
         <v>3000</v>
       </c>
-      <c r="T7" s="73"/>
-      <c r="U7" s="80" t="s">
+      <c r="T7" s="80"/>
+      <c r="U7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="80"/>
-      <c r="W7" s="81" t="s">
+      <c r="V7" s="76"/>
+      <c r="W7" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="X7" s="81"/>
+      <c r="X7" s="85"/>
       <c r="Z7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="AA7" s="84"/>
       <c r="AB7" s="84"/>
-      <c r="AC7" s="80"/>
-      <c r="AD7" s="80"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="81"/>
-    </row>
-    <row r="8" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC7" s="76"/>
+      <c r="AD7" s="76"/>
+      <c r="AE7" s="85"/>
+      <c r="AF7" s="85"/>
+    </row>
+    <row r="8" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="80">
         <v>9300</v>
       </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="80" t="s">
+      <c r="D8" s="80"/>
+      <c r="E8" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="80"/>
-      <c r="G8" s="81" t="s">
+      <c r="F8" s="76"/>
+      <c r="G8" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="81"/>
+      <c r="H8" s="85"/>
       <c r="J8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="86">
         <v>6300</v>
       </c>
-      <c r="L8" s="83"/>
-      <c r="M8" s="80" t="s">
+      <c r="L8" s="86"/>
+      <c r="M8" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="80"/>
-      <c r="O8" s="81" t="s">
+      <c r="N8" s="76"/>
+      <c r="O8" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="81"/>
+      <c r="P8" s="85"/>
       <c r="R8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S8" s="73">
+      <c r="S8" s="80">
         <v>3000</v>
       </c>
-      <c r="T8" s="73"/>
-      <c r="U8" s="80" t="s">
+      <c r="T8" s="80"/>
+      <c r="U8" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="V8" s="80"/>
-      <c r="W8" s="81" t="s">
+      <c r="V8" s="76"/>
+      <c r="W8" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="X8" s="81"/>
+      <c r="X8" s="85"/>
       <c r="Z8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="AA8" s="84"/>
       <c r="AB8" s="84"/>
-      <c r="AC8" s="80"/>
-      <c r="AD8" s="80"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="81"/>
-    </row>
-    <row r="9" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC8" s="76"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="85"/>
+      <c r="AF8" s="85"/>
+    </row>
+    <row r="9" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="73">
+      <c r="C9" s="80">
         <v>8500</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="80" t="s">
+      <c r="D9" s="80"/>
+      <c r="E9" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="80"/>
-      <c r="G9" s="81" t="s">
+      <c r="F9" s="76"/>
+      <c r="G9" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="81"/>
+      <c r="H9" s="85"/>
       <c r="J9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="86">
         <v>5500</v>
       </c>
-      <c r="L9" s="83"/>
-      <c r="M9" s="80" t="s">
+      <c r="L9" s="86"/>
+      <c r="M9" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="80"/>
-      <c r="O9" s="81" t="s">
+      <c r="N9" s="76"/>
+      <c r="O9" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="81"/>
+      <c r="P9" s="85"/>
       <c r="R9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S9" s="73">
+      <c r="S9" s="80">
         <v>3000</v>
       </c>
-      <c r="T9" s="73"/>
-      <c r="U9" s="80" t="s">
+      <c r="T9" s="80"/>
+      <c r="U9" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="V9" s="80"/>
-      <c r="W9" s="81" t="s">
+      <c r="V9" s="76"/>
+      <c r="W9" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="X9" s="81"/>
+      <c r="X9" s="85"/>
       <c r="Z9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AA9" s="84"/>
       <c r="AB9" s="84"/>
-      <c r="AC9" s="80"/>
-      <c r="AD9" s="80"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="81"/>
-    </row>
-    <row r="10" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="85"/>
+      <c r="AF9" s="85"/>
+    </row>
+    <row r="10" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="73">
+      <c r="C10" s="80">
         <v>7700</v>
       </c>
-      <c r="D10" s="73"/>
-      <c r="E10" s="85" t="s">
+      <c r="D10" s="80"/>
+      <c r="E10" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="85"/>
-      <c r="G10" s="86" t="s">
+      <c r="F10" s="78"/>
+      <c r="G10" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="86"/>
+      <c r="H10" s="79"/>
       <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="88">
+      <c r="K10" s="81">
         <v>4700</v>
       </c>
-      <c r="L10" s="88"/>
-      <c r="M10" s="85" t="s">
+      <c r="L10" s="81"/>
+      <c r="M10" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="85"/>
-      <c r="O10" s="86" t="s">
+      <c r="N10" s="78"/>
+      <c r="O10" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="86"/>
+      <c r="P10" s="79"/>
       <c r="R10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="S10" s="73">
+      <c r="S10" s="80">
         <v>3000</v>
       </c>
-      <c r="T10" s="73"/>
-      <c r="U10" s="85" t="s">
+      <c r="T10" s="80"/>
+      <c r="U10" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="V10" s="85"/>
-      <c r="W10" s="86" t="s">
+      <c r="V10" s="78"/>
+      <c r="W10" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="X10" s="86"/>
+      <c r="X10" s="79"/>
       <c r="Z10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AA10" s="87"/>
-      <c r="AB10" s="87"/>
-      <c r="AC10" s="85"/>
-      <c r="AD10" s="85"/>
-      <c r="AE10" s="86"/>
-      <c r="AF10" s="86"/>
-    </row>
-    <row r="11" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA10" s="77"/>
+      <c r="AB10" s="77"/>
+      <c r="AC10" s="78"/>
+      <c r="AD10" s="78"/>
+      <c r="AE10" s="79"/>
+      <c r="AF10" s="79"/>
+    </row>
+    <row r="11" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="73">
+      <c r="C11" s="80">
         <v>5200</v>
       </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="85" t="s">
+      <c r="D11" s="80"/>
+      <c r="E11" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="85"/>
-      <c r="G11" s="86" t="s">
+      <c r="F11" s="78"/>
+      <c r="G11" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="86"/>
+      <c r="H11" s="79"/>
       <c r="J11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="88">
+      <c r="K11" s="81">
         <v>42000</v>
       </c>
-      <c r="L11" s="88"/>
-      <c r="M11" s="89" t="s">
+      <c r="L11" s="81"/>
+      <c r="M11" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="89"/>
-      <c r="O11" s="90" t="s">
+      <c r="N11" s="82"/>
+      <c r="O11" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="90"/>
+      <c r="P11" s="83"/>
       <c r="R11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="S11" s="73">
+      <c r="S11" s="80">
         <v>21000</v>
       </c>
-      <c r="T11" s="73"/>
-      <c r="U11" s="85" t="s">
+      <c r="T11" s="80"/>
+      <c r="U11" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="V11" s="85"/>
-      <c r="W11" s="86" t="s">
+      <c r="V11" s="78"/>
+      <c r="W11" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="X11" s="86"/>
+      <c r="X11" s="79"/>
       <c r="Z11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="85"/>
-      <c r="AD11" s="85"/>
-      <c r="AE11" s="86"/>
-      <c r="AF11" s="86"/>
-    </row>
-    <row r="12" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y12" s="80"/>
-      <c r="Z12" s="80"/>
-      <c r="AA12" s="80"/>
-      <c r="AB12" s="80"/>
-      <c r="AC12" s="80"/>
-      <c r="AD12" s="80"/>
-    </row>
-    <row r="15" spans="2:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="AA11" s="77"/>
+      <c r="AB11" s="77"/>
+      <c r="AC11" s="78"/>
+      <c r="AD11" s="78"/>
+      <c r="AE11" s="79"/>
+      <c r="AF11" s="79"/>
+    </row>
+    <row r="12" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y12" s="76"/>
+      <c r="Z12" s="76"/>
+      <c r="AA12" s="76"/>
+      <c r="AB12" s="76"/>
+      <c r="AC12" s="76"/>
+      <c r="AD12" s="76"/>
+    </row>
+    <row r="15" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="2:32" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="9:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="9:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="9:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="9:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="9:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="9:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="I22" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="115">
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AC6:AD6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AD8"/>
+    <mergeCell ref="AE8:AF8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="Y12:Z12"/>
     <mergeCell ref="AA12:AB12"/>
     <mergeCell ref="AC12:AD12"/>
@@ -1936,97 +2027,6 @@
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="O10:P10"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AD8"/>
-    <mergeCell ref="AE8:AF8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="AE9:AF9"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AC5:AD5"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2036,9 +2036,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CRB111"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.5" style="7" customWidth="1"/>
+    <col min="1" max="1" width="45.44140625" style="7" customWidth="1"/>
     <col min="2" max="3" width="17.6640625" style="7" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" style="8" customWidth="1"/>
     <col min="5" max="6" width="8.6640625" style="7"/>
@@ -2046,7 +2046,7 @@
     <col min="8" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="9" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:64" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
@@ -2069,11 +2069,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:64" s="14" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
+    <row r="2" spans="1:64" s="14" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A2" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="91"/>
+      <c r="B2" s="94"/>
       <c r="D2" s="15"/>
       <c r="E2" s="14">
         <v>1</v>
@@ -2256,7 +2256,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
@@ -2272,7 +2272,7 @@
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
     </row>
-    <row r="4" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>25</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="G4" s="19"/>
       <c r="H4" s="19"/>
     </row>
-    <row r="5" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>26</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="I5" s="22"/>
       <c r="J5" s="22"/>
     </row>
-    <row r="6" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>27</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="D6" s="18"/>
       <c r="I6" s="19"/>
     </row>
-    <row r="7" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>29</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>30</v>
       </c>
@@ -2343,7 +2343,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>32</v>
       </c>
@@ -2357,7 +2357,7 @@
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="10" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>34</v>
       </c>
@@ -2371,7 +2371,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
     </row>
-    <row r="11" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>35</v>
       </c>
@@ -2387,7 +2387,7 @@
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
     </row>
-    <row r="12" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
@@ -2405,7 +2405,7 @@
       <c r="Q12" s="24"/>
       <c r="R12" s="24"/>
     </row>
-    <row r="13" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>37</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="T13" s="22"/>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>39</v>
       </c>
@@ -2434,7 +2434,7 @@
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
     </row>
-    <row r="15" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
         <v>40</v>
       </c>
@@ -2448,7 +2448,7 @@
       <c r="O15" s="19"/>
       <c r="P15" s="22"/>
     </row>
-    <row r="16" spans="1:64" ht="19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
         <v>42</v>
       </c>
@@ -2462,7 +2462,7 @@
       <c r="N16" s="24"/>
       <c r="O16" s="24"/>
     </row>
-    <row r="17" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
         <v>43</v>
       </c>
@@ -2477,7 +2477,7 @@
       <c r="W17" s="24"/>
       <c r="X17" s="24"/>
     </row>
-    <row r="18" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
         <v>45</v>
       </c>
@@ -2494,7 +2494,7 @@
       <c r="Y18" s="24"/>
       <c r="Z18" s="24"/>
     </row>
-    <row r="19" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
         <v>46</v>
       </c>
@@ -2510,7 +2510,7 @@
       <c r="AC19" s="24"/>
       <c r="AD19" s="24"/>
     </row>
-    <row r="20" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
         <v>48</v>
       </c>
@@ -2525,7 +2525,7 @@
       <c r="AF20" s="24"/>
       <c r="AG20" s="24"/>
     </row>
-    <row r="21" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
         <v>49</v>
       </c>
@@ -2539,14 +2539,14 @@
       <c r="AH21" s="24"/>
       <c r="AI21" s="24"/>
     </row>
-    <row r="22" spans="1:38" s="27" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" s="27" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A22" s="25" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="26"/>
       <c r="D22" s="28"/>
     </row>
-    <row r="23" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" s="16" t="s">
         <v>51</v>
       </c>
@@ -2560,7 +2560,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
     </row>
-    <row r="24" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
         <v>52</v>
       </c>
@@ -2575,7 +2575,7 @@
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
     </row>
-    <row r="25" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
         <v>53</v>
       </c>
@@ -2591,7 +2591,7 @@
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" s="16" t="s">
         <v>54</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" s="16" t="s">
         <v>55</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
     </row>
-    <row r="28" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
         <v>57</v>
       </c>
@@ -2637,7 +2637,7 @@
       <c r="D28" s="18"/>
       <c r="W28" s="19"/>
     </row>
-    <row r="29" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
         <v>58</v>
       </c>
@@ -2654,7 +2654,7 @@
       <c r="Z29" s="22"/>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
         <v>59</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="AC30" s="24"/>
       <c r="AD30" s="24"/>
     </row>
-    <row r="31" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
         <v>60</v>
       </c>
@@ -2687,7 +2687,7 @@
       <c r="AI31" s="24"/>
       <c r="AJ31" s="24"/>
     </row>
-    <row r="32" spans="1:38" ht="19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
         <v>61</v>
       </c>
@@ -2701,7 +2701,7 @@
       <c r="AK32" s="24"/>
       <c r="AL32" s="24"/>
     </row>
-    <row r="33" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
         <v>62</v>
       </c>
@@ -2716,7 +2716,7 @@
       <c r="AC33" s="24"/>
       <c r="AD33" s="24"/>
     </row>
-    <row r="34" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A34" s="16" t="s">
         <v>64</v>
       </c>
@@ -2732,7 +2732,7 @@
       <c r="AG34" s="24"/>
       <c r="AH34" s="24"/>
     </row>
-    <row r="35" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A35" s="16" t="s">
         <v>65</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="AR35" s="24"/>
       <c r="AS35" s="24"/>
     </row>
-    <row r="36" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A36" s="16" t="s">
         <v>67</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="AT36" s="24"/>
       <c r="AU36" s="24"/>
     </row>
-    <row r="37" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A37" s="16" t="s">
         <v>68</v>
       </c>
@@ -2784,7 +2784,7 @@
       <c r="AJ37" s="24"/>
       <c r="AK37" s="24"/>
     </row>
-    <row r="38" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A38" s="16" t="s">
         <v>69</v>
       </c>
@@ -2804,7 +2804,7 @@
       <c r="BB38" s="24"/>
       <c r="BC38" s="24"/>
     </row>
-    <row r="39" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
         <v>70</v>
       </c>
@@ -2822,14 +2822,14 @@
       <c r="BH39" s="24"/>
       <c r="BI39" s="24"/>
     </row>
-    <row r="40" spans="1:61" s="27" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:61" s="27" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="25" t="s">
         <v>71</v>
       </c>
       <c r="B40" s="26"/>
       <c r="D40" s="28"/>
     </row>
-    <row r="41" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
         <v>72</v>
       </c>
@@ -2843,7 +2843,7 @@
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
     </row>
-    <row r="42" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A42" s="16" t="s">
         <v>73</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
     </row>
-    <row r="43" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
         <v>74</v>
       </c>
@@ -2870,7 +2870,7 @@
       <c r="D43" s="30"/>
       <c r="I43" s="22"/>
     </row>
-    <row r="44" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
         <v>75</v>
       </c>
@@ -2886,7 +2886,7 @@
       <c r="K44" s="22"/>
       <c r="L44" s="22"/>
     </row>
-    <row r="45" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
         <v>76</v>
       </c>
@@ -2902,7 +2902,7 @@
       <c r="O45" s="22"/>
       <c r="P45" s="22"/>
     </row>
-    <row r="46" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
         <v>78</v>
       </c>
@@ -2916,7 +2916,7 @@
       <c r="Q46" s="24"/>
       <c r="R46" s="24"/>
     </row>
-    <row r="47" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
         <v>80</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="S47" s="24"/>
       <c r="T47" s="24"/>
     </row>
-    <row r="48" spans="1:61" ht="19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
         <v>81</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="U48" s="24"/>
       <c r="V48" s="24"/>
     </row>
-    <row r="49" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
         <v>82</v>
       </c>
@@ -2960,7 +2960,7 @@
       <c r="W49" s="24"/>
       <c r="X49" s="24"/>
     </row>
-    <row r="50" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A50" s="16" t="s">
         <v>83</v>
       </c>
@@ -2973,7 +2973,7 @@
       <c r="D50" s="31"/>
       <c r="Y50" s="24"/>
     </row>
-    <row r="51" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A51" s="16" t="s">
         <v>84</v>
       </c>
@@ -2989,7 +2989,7 @@
       <c r="AA51" s="24"/>
       <c r="AB51" s="24"/>
     </row>
-    <row r="52" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A52" s="16" t="s">
         <v>85</v>
       </c>
@@ -3005,7 +3005,7 @@
       <c r="AE52" s="24"/>
       <c r="AF52" s="24"/>
     </row>
-    <row r="53" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A53" s="16" t="s">
         <v>87</v>
       </c>
@@ -3019,7 +3019,7 @@
       <c r="AG53" s="24"/>
       <c r="AH53" s="24"/>
     </row>
-    <row r="54" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A54" s="16" t="s">
         <v>89</v>
       </c>
@@ -3035,7 +3035,7 @@
       <c r="AI54" s="24"/>
       <c r="AJ54" s="24"/>
     </row>
-    <row r="55" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A55" s="16" t="s">
         <v>90</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="AK55" s="24"/>
       <c r="AL55" s="24"/>
     </row>
-    <row r="56" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A56" s="16" t="s">
         <v>91</v>
       </c>
@@ -3063,7 +3063,7 @@
       <c r="AM56" s="24"/>
       <c r="AN56" s="24"/>
     </row>
-    <row r="57" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A57" s="16" t="s">
         <v>92</v>
       </c>
@@ -3076,7 +3076,7 @@
       <c r="D57" s="31"/>
       <c r="AO57" s="24"/>
     </row>
-    <row r="58" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
         <v>93</v>
       </c>
@@ -3092,7 +3092,7 @@
       <c r="AR58" s="24"/>
       <c r="AS58" s="24"/>
     </row>
-    <row r="59" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
         <v>95</v>
       </c>
@@ -3106,7 +3106,7 @@
       <c r="AT59" s="24"/>
       <c r="AU59" s="24"/>
     </row>
-    <row r="60" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
         <v>97</v>
       </c>
@@ -3122,14 +3122,14 @@
       <c r="AV60" s="24"/>
       <c r="AW60" s="24"/>
     </row>
-    <row r="61" spans="1:49" s="27" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:49" s="27" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A61" s="25" t="s">
         <v>98</v>
       </c>
       <c r="B61" s="26"/>
       <c r="D61" s="28"/>
     </row>
-    <row r="62" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>99</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="G62" s="32"/>
       <c r="H62" s="32"/>
     </row>
-    <row r="63" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>100</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="M63" s="33"/>
       <c r="N63" s="33"/>
     </row>
-    <row r="64" spans="1:49" ht="19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>101</v>
       </c>
@@ -3183,7 +3183,7 @@
       <c r="O64" s="33"/>
       <c r="P64" s="33"/>
     </row>
-    <row r="65" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>102</v>
       </c>
@@ -3203,7 +3203,7 @@
       <c r="W65" s="34"/>
       <c r="X65" s="34"/>
     </row>
-    <row r="66" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>103</v>
       </c>
@@ -3219,7 +3219,7 @@
       <c r="S66" s="34"/>
       <c r="T66" s="34"/>
     </row>
-    <row r="67" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>105</v>
       </c>
@@ -3239,7 +3239,7 @@
       <c r="W67" s="34"/>
       <c r="X67" s="34"/>
     </row>
-    <row r="68" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>106</v>
       </c>
@@ -3255,7 +3255,7 @@
       <c r="AA68" s="34"/>
       <c r="AB68" s="34"/>
     </row>
-    <row r="69" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>108</v>
       </c>
@@ -3271,7 +3271,7 @@
       <c r="AA69" s="34"/>
       <c r="AB69" s="34"/>
     </row>
-    <row r="70" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>109</v>
       </c>
@@ -3286,7 +3286,7 @@
       <c r="AD70" s="34"/>
       <c r="AE70" s="34"/>
     </row>
-    <row r="71" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>110</v>
       </c>
@@ -3301,7 +3301,7 @@
       <c r="AG71" s="34"/>
       <c r="AH71" s="34"/>
     </row>
-    <row r="72" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>112</v>
       </c>
@@ -3317,7 +3317,7 @@
       <c r="AK72" s="34"/>
       <c r="AL72" s="34"/>
     </row>
-    <row r="73" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>113</v>
       </c>
@@ -3333,14 +3333,14 @@
       <c r="AO73" s="34"/>
       <c r="AP73" s="34"/>
     </row>
-    <row r="74" spans="1:42" s="27" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" s="27" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A74" s="25" t="s">
         <v>114</v>
       </c>
       <c r="B74" s="35"/>
       <c r="D74" s="28"/>
     </row>
-    <row r="75" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
         <v>115</v>
       </c>
@@ -3351,15 +3351,15 @@
         <v>24</v>
       </c>
       <c r="D75" s="30"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
+      <c r="E75" s="72"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="72"/>
       <c r="H75" s="22"/>
       <c r="I75" s="22"/>
       <c r="J75" s="22"/>
       <c r="K75" s="22"/>
     </row>
-    <row r="76" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
         <v>116</v>
       </c>
@@ -3378,7 +3378,7 @@
       <c r="Q76" s="22"/>
       <c r="R76" s="22"/>
     </row>
-    <row r="77" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
         <v>117</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="R77" s="22"/>
       <c r="S77" s="24"/>
     </row>
-    <row r="78" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A78" s="16" t="s">
         <v>118</v>
       </c>
@@ -3414,7 +3414,7 @@
       <c r="U78" s="24"/>
       <c r="V78" s="24"/>
     </row>
-    <row r="79" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A79" s="16" t="s">
         <v>120</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="AA79" s="24"/>
       <c r="AB79" s="24"/>
     </row>
-    <row r="80" spans="1:42" ht="19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
         <v>121</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="AA80" s="24"/>
       <c r="AB80" s="24"/>
     </row>
-    <row r="81" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
         <v>122</v>
       </c>
@@ -3467,7 +3467,7 @@
       <c r="AF81" s="24"/>
       <c r="AG81" s="24"/>
     </row>
-    <row r="82" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
         <v>124</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="AL82" s="24"/>
       <c r="AM82" s="24"/>
     </row>
-    <row r="83" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
         <v>125</v>
       </c>
@@ -3501,7 +3501,7 @@
       <c r="AN83" s="24"/>
       <c r="AO83" s="24"/>
     </row>
-    <row r="84" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
         <v>126</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="AT84" s="24"/>
       <c r="AU84" s="24"/>
     </row>
-    <row r="85" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
         <v>128</v>
       </c>
@@ -3534,14 +3534,14 @@
       <c r="AW85" s="24"/>
       <c r="AX85" s="24"/>
     </row>
-    <row r="86" spans="1:50" s="27" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:50" s="27" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A86" s="25" t="s">
         <v>129</v>
       </c>
       <c r="B86" s="26"/>
       <c r="D86" s="28"/>
     </row>
-    <row r="87" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A87" s="16" t="s">
         <v>130</v>
       </c>
@@ -3576,7 +3576,7 @@
       <c r="Z87" s="38"/>
       <c r="AA87" s="38"/>
     </row>
-    <row r="88" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A88" s="16" t="s">
         <v>131</v>
       </c>
@@ -3588,10 +3588,10 @@
       </c>
       <c r="D88" s="39"/>
       <c r="E88" s="38"/>
-      <c r="F88" s="95"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="95"/>
-      <c r="I88" s="95"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="73"/>
+      <c r="H88" s="73"/>
+      <c r="I88" s="73"/>
       <c r="J88" s="38"/>
       <c r="K88" s="38"/>
       <c r="L88" s="38"/>
@@ -3611,7 +3611,7 @@
       <c r="Z88" s="38"/>
       <c r="AA88" s="38"/>
     </row>
-    <row r="89" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A89" s="16" t="s">
         <v>132</v>
       </c>
@@ -3623,10 +3623,10 @@
       </c>
       <c r="D89" s="39"/>
       <c r="E89" s="38"/>
-      <c r="F89" s="95"/>
-      <c r="G89" s="95"/>
-      <c r="H89" s="95"/>
-      <c r="I89" s="95"/>
+      <c r="F89" s="73"/>
+      <c r="G89" s="73"/>
+      <c r="H89" s="73"/>
+      <c r="I89" s="73"/>
       <c r="J89" s="38"/>
       <c r="K89" s="38"/>
       <c r="L89" s="38"/>
@@ -3646,7 +3646,7 @@
       <c r="Z89" s="38"/>
       <c r="AA89" s="38"/>
     </row>
-    <row r="90" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A90" s="16" t="s">
         <v>133</v>
       </c>
@@ -3658,10 +3658,10 @@
       </c>
       <c r="D90" s="39"/>
       <c r="E90" s="38"/>
-      <c r="F90" s="95"/>
-      <c r="G90" s="95"/>
-      <c r="H90" s="95"/>
-      <c r="I90" s="95"/>
+      <c r="F90" s="73"/>
+      <c r="G90" s="73"/>
+      <c r="H90" s="73"/>
+      <c r="I90" s="73"/>
       <c r="J90" s="38"/>
       <c r="K90" s="38"/>
       <c r="L90" s="38"/>
@@ -3681,7 +3681,7 @@
       <c r="Z90" s="38"/>
       <c r="AA90" s="38"/>
     </row>
-    <row r="91" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A91" s="16" t="s">
         <v>134</v>
       </c>
@@ -3697,14 +3697,14 @@
       <c r="G91" s="38"/>
       <c r="H91" s="38"/>
       <c r="I91" s="38"/>
-      <c r="J91" s="96"/>
-      <c r="K91" s="96"/>
-      <c r="L91" s="96"/>
-      <c r="M91" s="96"/>
-      <c r="N91" s="96"/>
-      <c r="O91" s="96"/>
-      <c r="P91" s="96"/>
-      <c r="Q91" s="96"/>
+      <c r="J91" s="74"/>
+      <c r="K91" s="74"/>
+      <c r="L91" s="74"/>
+      <c r="M91" s="74"/>
+      <c r="N91" s="74"/>
+      <c r="O91" s="74"/>
+      <c r="P91" s="74"/>
+      <c r="Q91" s="74"/>
       <c r="R91" s="38"/>
       <c r="S91" s="38"/>
       <c r="T91" s="38"/>
@@ -3716,7 +3716,7 @@
       <c r="Z91" s="38"/>
       <c r="AA91" s="38"/>
     </row>
-    <row r="92" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A92" s="16" t="s">
         <v>136</v>
       </c>
@@ -3732,8 +3732,8 @@
       <c r="G92" s="38"/>
       <c r="H92" s="38"/>
       <c r="I92" s="38"/>
-      <c r="J92" s="96"/>
-      <c r="K92" s="96"/>
+      <c r="J92" s="74"/>
+      <c r="K92" s="74"/>
       <c r="L92" s="38"/>
       <c r="M92" s="38"/>
       <c r="N92" s="38"/>
@@ -3749,7 +3749,7 @@
       <c r="Z92" s="38"/>
       <c r="AA92" s="38"/>
     </row>
-    <row r="93" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A93" s="16" t="s">
         <v>138</v>
       </c>
@@ -3773,8 +3773,8 @@
       <c r="O93" s="38"/>
       <c r="P93" s="38"/>
       <c r="Q93" s="38"/>
-      <c r="R93" s="97"/>
-      <c r="S93" s="97"/>
+      <c r="R93" s="75"/>
+      <c r="S93" s="75"/>
       <c r="V93" s="38"/>
       <c r="W93" s="38"/>
       <c r="X93" s="38"/>
@@ -3782,7 +3782,7 @@
       <c r="Z93" s="38"/>
       <c r="AA93" s="38"/>
     </row>
-    <row r="94" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A94" s="16" t="s">
         <v>139</v>
       </c>
@@ -3817,7 +3817,7 @@
       <c r="Z94" s="38"/>
       <c r="AA94" s="38"/>
     </row>
-    <row r="95" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A95" s="16" t="s">
         <v>141</v>
       </c>
@@ -3852,7 +3852,7 @@
       <c r="X95" s="41"/>
       <c r="Y95" s="41"/>
     </row>
-    <row r="96" spans="1:50" ht="19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A96" s="16" t="s">
         <v>142</v>
       </c>
@@ -3866,7 +3866,7 @@
       <c r="X96" s="34"/>
       <c r="Y96" s="34"/>
     </row>
-    <row r="97" spans="1:2498" ht="19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A97" s="16" t="s">
         <v>143</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="AH97" s="34"/>
       <c r="AI97" s="34"/>
     </row>
-    <row r="98" spans="1:2498" ht="19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>144</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="D98" s="42"/>
       <c r="AI98" s="34"/>
     </row>
-    <row r="99" spans="1:2498" ht="19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>145</v>
       </c>
@@ -3918,7 +3918,7 @@
       <c r="AM99" s="34"/>
       <c r="AN99" s="34"/>
     </row>
-    <row r="100" spans="1:2498" s="43" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2498" s="43" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>146</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="AO100" s="34"/>
       <c r="AP100" s="34"/>
     </row>
-    <row r="101" spans="1:2498" s="44" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2498" s="44" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A101" s="25" t="s">
         <v>147</v>
       </c>
@@ -6434,7 +6434,7 @@
       <c r="CRA101" s="27"/>
       <c r="CRB101" s="27"/>
     </row>
-    <row r="102" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A102" s="45" t="s">
         <v>148</v>
       </c>
@@ -6448,7 +6448,7 @@
       <c r="E102" s="19"/>
       <c r="F102" s="19"/>
     </row>
-    <row r="103" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A103" s="45" t="s">
         <v>149</v>
       </c>
@@ -6465,7 +6465,7 @@
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
     </row>
-    <row r="104" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A104" s="45" t="s">
         <v>150</v>
       </c>
@@ -6482,7 +6482,7 @@
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
     </row>
-    <row r="105" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A105" s="45" t="s">
         <v>151</v>
       </c>
@@ -6499,7 +6499,7 @@
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
     </row>
-    <row r="106" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A106" s="45" t="s">
         <v>152</v>
       </c>
@@ -6524,7 +6524,7 @@
       <c r="R106" s="22"/>
       <c r="S106" s="22"/>
     </row>
-    <row r="107" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A107" s="45" t="s">
         <v>153</v>
       </c>
@@ -6541,7 +6541,7 @@
       <c r="W107" s="24"/>
       <c r="X107" s="24"/>
     </row>
-    <row r="108" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A108" s="45" t="s">
         <v>155</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="AB108" s="24"/>
       <c r="AC108" s="24"/>
     </row>
-    <row r="109" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A109" s="45" t="s">
         <v>156</v>
       </c>
@@ -6576,7 +6576,7 @@
       <c r="AH109" s="24"/>
       <c r="AI109" s="24"/>
     </row>
-    <row r="110" spans="1:2498" ht="20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2498" x14ac:dyDescent="0.35">
       <c r="A110" s="45" t="s">
         <v>157</v>
       </c>
@@ -6594,7 +6594,7 @@
       <c r="AN110" s="24"/>
       <c r="AO110" s="24"/>
     </row>
-    <row r="111" spans="1:2498" s="44" customFormat="1" ht="20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2498" s="44" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="47" t="s">
         <v>159</v>
       </c>
@@ -6622,294 +6622,294 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:S15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="92" t="s">
+    <row r="2" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92" t="s">
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92" t="s">
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92" t="s">
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92" t="s">
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92" t="s">
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97" t="s">
         <v>165</v>
       </c>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="93" t="s">
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93" t="s">
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93" t="s">
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93" t="s">
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93" t="s">
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93" t="s">
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-    </row>
-    <row r="5" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
-      <c r="S5" s="94"/>
-    </row>
-    <row r="6" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="94"/>
-      <c r="N6" s="94"/>
-      <c r="O6" s="94"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
-      <c r="S6" s="94"/>
-    </row>
-    <row r="7" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
-      <c r="S7" s="94"/>
-    </row>
-    <row r="8" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
-      <c r="S8" s="94"/>
-    </row>
-    <row r="9" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
-      <c r="S9" s="94"/>
-    </row>
-    <row r="10" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
-      <c r="S10" s="94"/>
-    </row>
-    <row r="11" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
-      <c r="S11" s="94"/>
-    </row>
-    <row r="12" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="94"/>
-    </row>
-    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
-      <c r="S13" s="94"/>
-    </row>
-    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="95"/>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="95"/>
+      <c r="S4" s="95"/>
+    </row>
+    <row r="5" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+    </row>
+    <row r="6" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="95"/>
+      <c r="Q6" s="95"/>
+      <c r="R6" s="95"/>
+      <c r="S6" s="95"/>
+    </row>
+    <row r="7" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="95"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+    </row>
+    <row r="8" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="95"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="95"/>
+      <c r="P8" s="95"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="95"/>
+    </row>
+    <row r="9" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="95"/>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
+      <c r="S9" s="95"/>
+    </row>
+    <row r="10" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="95"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95"/>
+      <c r="P10" s="95"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="95"/>
+    </row>
+    <row r="11" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="95"/>
+      <c r="N11" s="95"/>
+      <c r="O11" s="95"/>
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+    </row>
+    <row r="12" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="95"/>
+      <c r="O12" s="95"/>
+      <c r="P12" s="95"/>
+      <c r="Q12" s="95"/>
+      <c r="R12" s="95"/>
+      <c r="S12" s="95"/>
+    </row>
+    <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="95"/>
+      <c r="P13" s="95"/>
+      <c r="Q13" s="95"/>
+      <c r="R13" s="95"/>
+      <c r="S13" s="95"/>
+    </row>
+    <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="51"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="93"/>
-      <c r="P14" s="93"/>
-      <c r="Q14" s="93"/>
-      <c r="R14" s="93"/>
-      <c r="S14" s="93"/>
-    </row>
-    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+    </row>
+    <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="52" t="s">
         <v>167</v>
       </c>
@@ -6924,6 +6924,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q4:S13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
@@ -6936,18 +6948,6 @@
     <mergeCell ref="H4:J13"/>
     <mergeCell ref="K4:M13"/>
     <mergeCell ref="N4:P13"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6957,12 +6957,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:O12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B2" s="54"/>
       <c r="C2" s="55" t="s">
         <v>168</v>
@@ -6985,7 +6985,7 @@
       <c r="K2" s="56"/>
       <c r="L2" s="57"/>
     </row>
-    <row r="3" spans="2:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B3" s="54"/>
       <c r="C3" s="58" t="s">
         <v>173</v>
@@ -7008,7 +7008,7 @@
       <c r="K3" s="59"/>
       <c r="L3" s="60"/>
     </row>
-    <row r="4" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="54" t="s">
         <v>177</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="K4" s="62"/>
       <c r="L4" s="63"/>
     </row>
-    <row r="5" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="64" t="s">
         <v>7</v>
       </c>
@@ -7058,7 +7058,7 @@
       <c r="K5" s="65"/>
       <c r="L5" s="65"/>
     </row>
-    <row r="6" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="66" t="s">
         <v>9</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="66" t="s">
         <v>178</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="66" t="s">
         <v>11</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="66" t="s">
         <v>179</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="66" t="s">
         <v>13</v>
       </c>
@@ -7195,7 +7195,7 @@
       <c r="K10" s="65"/>
       <c r="L10" s="65"/>
     </row>
-    <row r="11" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="67" t="s">
         <v>14</v>
       </c>
@@ -7220,7 +7220,7 @@
       <c r="K11" s="54"/>
       <c r="L11" s="54"/>
     </row>
-    <row r="12" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="68" t="s">
         <v>0</v>
       </c>
